--- a/MASTER_MS5673.xlsx
+++ b/MASTER_MS5673.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer_CA\＊Strim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F764C94-0299-4575-BACA-1C3030F1CD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4082D79E-5D33-47BB-A0FE-251967AEA4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="19815" windowHeight="13845" tabRatio="773" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
+    <workbookView xWindow="4425" yWindow="900" windowWidth="19815" windowHeight="13845" tabRatio="773" activeTab="2" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="3" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10528" uniqueCount="4712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10549" uniqueCount="4721">
   <si>
     <t>무역거래처상호</t>
   </si>
@@ -16595,6 +16595,39 @@
   </si>
   <si>
     <t>XU102866-22003C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-124441 (DFPW0456B8UY004)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AVC-FAN,50VDC,4356MM,DUAL,ROTE, VOLT:DC50V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-124441</t>
+  </si>
+  <si>
+    <t>MSF-124439</t>
+  </si>
+  <si>
+    <t>MSF-124439 (M1283205-002)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WIWYNN-PCBA+MECH,MAIN BOARD,HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-077655</t>
+  </si>
+  <si>
+    <t>MSF-077655 (M1203074-001)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUANTA-PCBA+MECH,MOTHERBOARD,C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17069,7 +17102,67 @@
     <cellStyle name="표준 2" xfId="1" xr:uid="{04AB7DDF-CEE2-4E84-BB25-B76053D24319}"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="88">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18602,7 +18695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}">
-  <dimension ref="A1:N1160"/>
+  <dimension ref="A1:N1163"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
@@ -38602,45 +38695,78 @@
         <v>4709</v>
       </c>
     </row>
+    <row r="1161" spans="2:4">
+      <c r="B1161" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>4712</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="1162" spans="2:4">
+      <c r="B1162" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>4716</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>4717</v>
+      </c>
+    </row>
+    <row r="1163" spans="2:4">
+      <c r="B1163" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>4719</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>4720</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1160" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C995">
-    <cfRule type="duplicateValues" dxfId="81" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C996">
-    <cfRule type="duplicateValues" dxfId="80" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C2:C992 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="79" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="78" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1118">
-    <cfRule type="duplicateValues" dxfId="77" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1127">
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1137">
-    <cfRule type="duplicateValues" dxfId="75" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709">
-    <cfRule type="duplicateValues" dxfId="74" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E769">
-    <cfRule type="duplicateValues" dxfId="72" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E788">
-    <cfRule type="duplicateValues" dxfId="70" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E832">
-    <cfRule type="duplicateValues" dxfId="68" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42057,7 +42183,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB924F-9221-4917-B11B-3326F8C1F68D}">
-  <dimension ref="A1:N316"/>
+  <dimension ref="A1:N319"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
@@ -48400,117 +48526,177 @@
         <v>4709</v>
       </c>
     </row>
+    <row r="317" spans="2:5">
+      <c r="B317" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C317" t="s">
+        <v>4714</v>
+      </c>
+      <c r="D317" t="s">
+        <v>4712</v>
+      </c>
+      <c r="E317" t="s">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="318" spans="2:5">
+      <c r="B318" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C318" t="s">
+        <v>4715</v>
+      </c>
+      <c r="D318" t="s">
+        <v>4716</v>
+      </c>
+      <c r="E318" t="s">
+        <v>4717</v>
+      </c>
+    </row>
+    <row r="319" spans="2:5">
+      <c r="B319" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C319" t="s">
+        <v>4718</v>
+      </c>
+      <c r="D319" t="s">
+        <v>4719</v>
+      </c>
+      <c r="E319" t="s">
+        <v>4720</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D2:D265">
-    <cfRule type="duplicateValues" dxfId="66" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D259:D265">
-    <cfRule type="duplicateValues" dxfId="65" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D279">
+    <cfRule type="duplicateValues" dxfId="70" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D281">
+    <cfRule type="duplicateValues" dxfId="68" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D286">
+    <cfRule type="duplicateValues" dxfId="66" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D287:D288">
     <cfRule type="duplicateValues" dxfId="64" priority="50"/>
     <cfRule type="duplicateValues" dxfId="63" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D281">
+  <conditionalFormatting sqref="D290">
     <cfRule type="duplicateValues" dxfId="62" priority="48"/>
     <cfRule type="duplicateValues" dxfId="61" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D286">
+  <conditionalFormatting sqref="D292">
     <cfRule type="duplicateValues" dxfId="60" priority="46"/>
     <cfRule type="duplicateValues" dxfId="59" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D287:D288">
+  <conditionalFormatting sqref="D293">
     <cfRule type="duplicateValues" dxfId="58" priority="44"/>
     <cfRule type="duplicateValues" dxfId="57" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D290">
+  <conditionalFormatting sqref="D294">
     <cfRule type="duplicateValues" dxfId="56" priority="42"/>
     <cfRule type="duplicateValues" dxfId="55" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D292">
+  <conditionalFormatting sqref="D295">
     <cfRule type="duplicateValues" dxfId="54" priority="40"/>
     <cfRule type="duplicateValues" dxfId="53" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D293">
+  <conditionalFormatting sqref="D296">
     <cfRule type="duplicateValues" dxfId="52" priority="38"/>
     <cfRule type="duplicateValues" dxfId="51" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D294">
+  <conditionalFormatting sqref="D298">
     <cfRule type="duplicateValues" dxfId="50" priority="36"/>
     <cfRule type="duplicateValues" dxfId="49" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D295">
+  <conditionalFormatting sqref="D299">
     <cfRule type="duplicateValues" dxfId="48" priority="34"/>
     <cfRule type="duplicateValues" dxfId="47" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D296">
+  <conditionalFormatting sqref="D300">
     <cfRule type="duplicateValues" dxfId="46" priority="32"/>
     <cfRule type="duplicateValues" dxfId="45" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D298">
-    <cfRule type="duplicateValues" dxfId="44" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D299">
-    <cfRule type="duplicateValues" dxfId="42" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D300">
-    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="27"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D301">
-    <cfRule type="duplicateValues" dxfId="38" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D302">
+    <cfRule type="duplicateValues" dxfId="43" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D303">
+    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D304">
+    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D306">
     <cfRule type="duplicateValues" dxfId="37" priority="23"/>
     <cfRule type="duplicateValues" dxfId="36" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D303">
+  <conditionalFormatting sqref="D308">
     <cfRule type="duplicateValues" dxfId="35" priority="21"/>
     <cfRule type="duplicateValues" dxfId="34" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D304">
+  <conditionalFormatting sqref="D310">
     <cfRule type="duplicateValues" dxfId="33" priority="19"/>
     <cfRule type="duplicateValues" dxfId="32" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D306">
+  <conditionalFormatting sqref="D311">
     <cfRule type="duplicateValues" dxfId="31" priority="17"/>
     <cfRule type="duplicateValues" dxfId="30" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D308">
+  <conditionalFormatting sqref="D312">
     <cfRule type="duplicateValues" dxfId="29" priority="15"/>
     <cfRule type="duplicateValues" dxfId="28" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D310">
+  <conditionalFormatting sqref="D313">
     <cfRule type="duplicateValues" dxfId="27" priority="13"/>
     <cfRule type="duplicateValues" dxfId="26" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D311">
+  <conditionalFormatting sqref="D314">
     <cfRule type="duplicateValues" dxfId="25" priority="11"/>
     <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D312">
+  <conditionalFormatting sqref="D315">
     <cfRule type="duplicateValues" dxfId="23" priority="9"/>
     <cfRule type="duplicateValues" dxfId="22" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D313">
-    <cfRule type="duplicateValues" dxfId="21" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D314">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D315">
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+  <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="21" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D317">
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D317">
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D318">
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D318">
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D319">
     <cfRule type="duplicateValues" dxfId="15" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C316:D316">
+  <conditionalFormatting sqref="D319">
     <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER_MS5673.xlsx
+++ b/MASTER_MS5673.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer_CA\＊Strim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4082D79E-5D33-47BB-A0FE-251967AEA4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CB3830-3B6B-4D87-BEFA-45D543EF4555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4425" yWindow="900" windowWidth="19815" windowHeight="13845" tabRatio="773" activeTab="2" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10549" uniqueCount="4721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10563" uniqueCount="4727">
   <si>
     <t>무역거래처상호</t>
   </si>
@@ -16628,6 +16628,30 @@
   </si>
   <si>
     <t>QUANTA-PCBA+MECH,MOTHERBOARD,C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-105556 (M1291207-001)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-106698 (HMCGM4MGBRB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYNIX-SSDASSY,E1.S,15MM,NVME,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HYNIX-MMOD,RDIMM,96GB,SM,DDR5 MODEL:100-000000815</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-105556</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-106698</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17102,7 +17126,27 @@
     <cellStyle name="표준 2" xfId="1" xr:uid="{04AB7DDF-CEE2-4E84-BB25-B76053D24319}"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="88">
+  <dxfs count="90">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18695,7 +18739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}">
-  <dimension ref="A1:N1163"/>
+  <dimension ref="A1:N1166"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
@@ -38728,45 +38772,70 @@
         <v>4720</v>
       </c>
     </row>
+    <row r="1164" spans="2:4">
+      <c r="B1164" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>4721</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>4723</v>
+      </c>
+    </row>
+    <row r="1165" spans="2:4">
+      <c r="B1165" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>4722</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="1166" spans="2:4">
+      <c r="B1166" s="1"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1160" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C995">
-    <cfRule type="duplicateValues" dxfId="87" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C996">
-    <cfRule type="duplicateValues" dxfId="86" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C2:C992 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="85" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="84" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1118">
-    <cfRule type="duplicateValues" dxfId="83" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1127">
-    <cfRule type="duplicateValues" dxfId="82" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1137">
-    <cfRule type="duplicateValues" dxfId="81" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709">
-    <cfRule type="duplicateValues" dxfId="80" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E769">
-    <cfRule type="duplicateValues" dxfId="78" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E788">
-    <cfRule type="duplicateValues" dxfId="76" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E832">
-    <cfRule type="duplicateValues" dxfId="74" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -42183,7 +42252,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB924F-9221-4917-B11B-3326F8C1F68D}">
-  <dimension ref="A1:N319"/>
+  <dimension ref="A1:N321"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
@@ -48568,135 +48637,169 @@
         <v>4720</v>
       </c>
     </row>
+    <row r="320" spans="2:5">
+      <c r="B320" s="1" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C320" t="s">
+        <v>4725</v>
+      </c>
+      <c r="D320" t="s">
+        <v>4721</v>
+      </c>
+      <c r="E320" t="s">
+        <v>4723</v>
+      </c>
+    </row>
+    <row r="321" spans="2:5">
+      <c r="B321" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C321" t="s">
+        <v>4726</v>
+      </c>
+      <c r="D321" t="s">
+        <v>4722</v>
+      </c>
+      <c r="E321" t="s">
+        <v>4724</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D2:D265">
-    <cfRule type="duplicateValues" dxfId="72" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D259:D265">
-    <cfRule type="duplicateValues" dxfId="71" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D279">
+    <cfRule type="duplicateValues" dxfId="72" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D281">
     <cfRule type="duplicateValues" dxfId="70" priority="56"/>
     <cfRule type="duplicateValues" dxfId="69" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D281">
+  <conditionalFormatting sqref="D286">
     <cfRule type="duplicateValues" dxfId="68" priority="54"/>
     <cfRule type="duplicateValues" dxfId="67" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D286">
+  <conditionalFormatting sqref="D287:D288">
     <cfRule type="duplicateValues" dxfId="66" priority="52"/>
     <cfRule type="duplicateValues" dxfId="65" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D287:D288">
+  <conditionalFormatting sqref="D290">
     <cfRule type="duplicateValues" dxfId="64" priority="50"/>
     <cfRule type="duplicateValues" dxfId="63" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D290">
+  <conditionalFormatting sqref="D292">
     <cfRule type="duplicateValues" dxfId="62" priority="48"/>
     <cfRule type="duplicateValues" dxfId="61" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D292">
+  <conditionalFormatting sqref="D293">
     <cfRule type="duplicateValues" dxfId="60" priority="46"/>
     <cfRule type="duplicateValues" dxfId="59" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D293">
+  <conditionalFormatting sqref="D294">
     <cfRule type="duplicateValues" dxfId="58" priority="44"/>
     <cfRule type="duplicateValues" dxfId="57" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D294">
+  <conditionalFormatting sqref="D295">
     <cfRule type="duplicateValues" dxfId="56" priority="42"/>
     <cfRule type="duplicateValues" dxfId="55" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D295">
+  <conditionalFormatting sqref="D296">
     <cfRule type="duplicateValues" dxfId="54" priority="40"/>
     <cfRule type="duplicateValues" dxfId="53" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D296">
+  <conditionalFormatting sqref="D298">
     <cfRule type="duplicateValues" dxfId="52" priority="38"/>
     <cfRule type="duplicateValues" dxfId="51" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D298">
+  <conditionalFormatting sqref="D299">
     <cfRule type="duplicateValues" dxfId="50" priority="36"/>
     <cfRule type="duplicateValues" dxfId="49" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D299">
+  <conditionalFormatting sqref="D300">
     <cfRule type="duplicateValues" dxfId="48" priority="34"/>
     <cfRule type="duplicateValues" dxfId="47" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D300">
-    <cfRule type="duplicateValues" dxfId="46" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="33"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D301">
-    <cfRule type="duplicateValues" dxfId="44" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D302">
+    <cfRule type="duplicateValues" dxfId="45" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D303">
     <cfRule type="duplicateValues" dxfId="43" priority="29"/>
     <cfRule type="duplicateValues" dxfId="42" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D303">
+  <conditionalFormatting sqref="D304">
     <cfRule type="duplicateValues" dxfId="41" priority="27"/>
     <cfRule type="duplicateValues" dxfId="40" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D304">
+  <conditionalFormatting sqref="D306">
     <cfRule type="duplicateValues" dxfId="39" priority="25"/>
     <cfRule type="duplicateValues" dxfId="38" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D306">
+  <conditionalFormatting sqref="D308">
     <cfRule type="duplicateValues" dxfId="37" priority="23"/>
     <cfRule type="duplicateValues" dxfId="36" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D308">
+  <conditionalFormatting sqref="D310">
     <cfRule type="duplicateValues" dxfId="35" priority="21"/>
     <cfRule type="duplicateValues" dxfId="34" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D310">
+  <conditionalFormatting sqref="D311">
     <cfRule type="duplicateValues" dxfId="33" priority="19"/>
     <cfRule type="duplicateValues" dxfId="32" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D311">
+  <conditionalFormatting sqref="D312">
     <cfRule type="duplicateValues" dxfId="31" priority="17"/>
     <cfRule type="duplicateValues" dxfId="30" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D312">
+  <conditionalFormatting sqref="D313">
     <cfRule type="duplicateValues" dxfId="29" priority="15"/>
     <cfRule type="duplicateValues" dxfId="28" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D313">
+  <conditionalFormatting sqref="D314">
     <cfRule type="duplicateValues" dxfId="27" priority="13"/>
     <cfRule type="duplicateValues" dxfId="26" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D314">
+  <conditionalFormatting sqref="D315">
     <cfRule type="duplicateValues" dxfId="25" priority="11"/>
     <cfRule type="duplicateValues" dxfId="24" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D315">
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+  <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D317">
     <cfRule type="duplicateValues" dxfId="21" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C316:D316">
+  <conditionalFormatting sqref="D317">
     <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D317">
+  <conditionalFormatting sqref="D318">
     <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D317">
+  <conditionalFormatting sqref="D318">
     <cfRule type="duplicateValues" dxfId="18" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318">
+  <conditionalFormatting sqref="D319">
     <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318">
+  <conditionalFormatting sqref="D319">
     <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D319">
+  <conditionalFormatting sqref="D320:D321">
     <cfRule type="duplicateValues" dxfId="15" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D319">
+  <conditionalFormatting sqref="D320:D321">
     <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER_MS5673.xlsx
+++ b/MASTER_MS5673.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer_CA\＊Strim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFDC730-3F3C-4021-A16A-62A9A08CACCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE831CF-04FA-44D0-A34C-8CD4DCCFC75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="900" windowWidth="19815" windowHeight="13845" tabRatio="773" activeTab="1" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
+    <workbookView xWindow="4425" yWindow="900" windowWidth="19815" windowHeight="13845" tabRatio="773" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="3" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10592" uniqueCount="4740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10606" uniqueCount="4746">
   <si>
     <t>무역거래처상호</t>
   </si>
@@ -16705,6 +16705,28 @@
   <si>
     <t>MSF-106873</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-077324 (DFPK0456B2GY0Q2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AVC-FAN,13.2VDC,DUAL ROTOR,40X VOLT:DC13.2V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073174 (GFM0412SS-1028D)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELTA-FAN,13.2VDC,L80MM 4056 F VOLT:DC13.2V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-077324</t>
+  </si>
+  <si>
+    <t>MSF-073174</t>
   </si>
 </sst>
 </file>
@@ -17178,7 +17200,27 @@
     <cellStyle name="표준 2" xfId="1" xr:uid="{04AB7DDF-CEE2-4E84-BB25-B76053D24319}"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="92">
+  <dxfs count="94">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18811,7 +18853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}">
-  <dimension ref="A1:N1169"/>
+  <dimension ref="A1:N1171"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
@@ -38913,45 +38955,67 @@
         <v>4735</v>
       </c>
     </row>
+    <row r="1170" spans="2:4">
+      <c r="B1170" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>4740</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="1171" spans="2:4">
+      <c r="B1171" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>4742</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>4743</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1160" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C995">
-    <cfRule type="duplicateValues" dxfId="91" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C996">
-    <cfRule type="duplicateValues" dxfId="90" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C2:C992 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="89" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="88" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1118">
-    <cfRule type="duplicateValues" dxfId="87" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1127">
-    <cfRule type="duplicateValues" dxfId="86" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1137">
-    <cfRule type="duplicateValues" dxfId="85" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709">
-    <cfRule type="duplicateValues" dxfId="84" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E769">
-    <cfRule type="duplicateValues" dxfId="82" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E788">
-    <cfRule type="duplicateValues" dxfId="80" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E832">
-    <cfRule type="duplicateValues" dxfId="78" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -39163,7 +39227,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB924F-9221-4917-B11B-3326F8C1F68D}">
-  <dimension ref="A1:N325"/>
+  <dimension ref="A1:N327"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
@@ -45632,147 +45696,181 @@
         <v>4735</v>
       </c>
     </row>
+    <row r="326" spans="2:5">
+      <c r="B326" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C326" t="s">
+        <v>4744</v>
+      </c>
+      <c r="D326" t="s">
+        <v>4740</v>
+      </c>
+      <c r="E326" t="s">
+        <v>4741</v>
+      </c>
+    </row>
+    <row r="327" spans="2:5">
+      <c r="B327" s="1" t="s">
+        <v>3406</v>
+      </c>
+      <c r="C327" t="s">
+        <v>4745</v>
+      </c>
+      <c r="D327" t="s">
+        <v>4742</v>
+      </c>
+      <c r="E327" t="s">
+        <v>4743</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D2:D265">
-    <cfRule type="duplicateValues" dxfId="76" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D259:D265">
-    <cfRule type="duplicateValues" dxfId="75" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D279">
+    <cfRule type="duplicateValues" dxfId="76" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D281">
     <cfRule type="duplicateValues" dxfId="74" priority="60"/>
     <cfRule type="duplicateValues" dxfId="73" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D281">
+  <conditionalFormatting sqref="D286">
     <cfRule type="duplicateValues" dxfId="72" priority="58"/>
     <cfRule type="duplicateValues" dxfId="71" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D286">
+  <conditionalFormatting sqref="D287:D288">
     <cfRule type="duplicateValues" dxfId="70" priority="56"/>
     <cfRule type="duplicateValues" dxfId="69" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D287:D288">
+  <conditionalFormatting sqref="D290">
     <cfRule type="duplicateValues" dxfId="68" priority="54"/>
     <cfRule type="duplicateValues" dxfId="67" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D290">
+  <conditionalFormatting sqref="D292">
     <cfRule type="duplicateValues" dxfId="66" priority="52"/>
     <cfRule type="duplicateValues" dxfId="65" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D292">
+  <conditionalFormatting sqref="D293">
     <cfRule type="duplicateValues" dxfId="64" priority="50"/>
     <cfRule type="duplicateValues" dxfId="63" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D293">
+  <conditionalFormatting sqref="D294">
     <cfRule type="duplicateValues" dxfId="62" priority="48"/>
     <cfRule type="duplicateValues" dxfId="61" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D294">
+  <conditionalFormatting sqref="D295">
     <cfRule type="duplicateValues" dxfId="60" priority="46"/>
     <cfRule type="duplicateValues" dxfId="59" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D295">
+  <conditionalFormatting sqref="D296">
     <cfRule type="duplicateValues" dxfId="58" priority="44"/>
     <cfRule type="duplicateValues" dxfId="57" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D296">
+  <conditionalFormatting sqref="D298">
     <cfRule type="duplicateValues" dxfId="56" priority="42"/>
     <cfRule type="duplicateValues" dxfId="55" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D298">
+  <conditionalFormatting sqref="D299">
     <cfRule type="duplicateValues" dxfId="54" priority="40"/>
     <cfRule type="duplicateValues" dxfId="53" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D299">
+  <conditionalFormatting sqref="D300">
     <cfRule type="duplicateValues" dxfId="52" priority="38"/>
     <cfRule type="duplicateValues" dxfId="51" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D300">
-    <cfRule type="duplicateValues" dxfId="50" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="37"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D301">
-    <cfRule type="duplicateValues" dxfId="48" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D302">
+    <cfRule type="duplicateValues" dxfId="49" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D303">
     <cfRule type="duplicateValues" dxfId="47" priority="33"/>
     <cfRule type="duplicateValues" dxfId="46" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D303">
+  <conditionalFormatting sqref="D304">
     <cfRule type="duplicateValues" dxfId="45" priority="31"/>
     <cfRule type="duplicateValues" dxfId="44" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D304">
+  <conditionalFormatting sqref="D306">
     <cfRule type="duplicateValues" dxfId="43" priority="29"/>
     <cfRule type="duplicateValues" dxfId="42" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D306">
+  <conditionalFormatting sqref="D308">
     <cfRule type="duplicateValues" dxfId="41" priority="27"/>
     <cfRule type="duplicateValues" dxfId="40" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D308">
+  <conditionalFormatting sqref="D310">
     <cfRule type="duplicateValues" dxfId="39" priority="25"/>
     <cfRule type="duplicateValues" dxfId="38" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D310">
+  <conditionalFormatting sqref="D311">
     <cfRule type="duplicateValues" dxfId="37" priority="23"/>
     <cfRule type="duplicateValues" dxfId="36" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D311">
+  <conditionalFormatting sqref="D312">
     <cfRule type="duplicateValues" dxfId="35" priority="21"/>
     <cfRule type="duplicateValues" dxfId="34" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D312">
+  <conditionalFormatting sqref="D313">
     <cfRule type="duplicateValues" dxfId="33" priority="19"/>
     <cfRule type="duplicateValues" dxfId="32" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D313">
+  <conditionalFormatting sqref="D314">
     <cfRule type="duplicateValues" dxfId="31" priority="17"/>
     <cfRule type="duplicateValues" dxfId="30" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D314">
+  <conditionalFormatting sqref="D315">
     <cfRule type="duplicateValues" dxfId="29" priority="15"/>
     <cfRule type="duplicateValues" dxfId="28" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D315">
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+  <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D317">
     <cfRule type="duplicateValues" dxfId="25" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C316:D316">
+  <conditionalFormatting sqref="D317">
     <cfRule type="duplicateValues" dxfId="24" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D317">
+  <conditionalFormatting sqref="D318">
     <cfRule type="duplicateValues" dxfId="23" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D317">
+  <conditionalFormatting sqref="D318">
     <cfRule type="duplicateValues" dxfId="22" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318">
+  <conditionalFormatting sqref="D319">
     <cfRule type="duplicateValues" dxfId="21" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318">
+  <conditionalFormatting sqref="D319">
     <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D319">
+  <conditionalFormatting sqref="D320:D321">
     <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D319">
+  <conditionalFormatting sqref="D320:D321">
     <cfRule type="duplicateValues" dxfId="18" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D320:D321">
+  <conditionalFormatting sqref="D322:D325">
     <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D320:D321">
+  <conditionalFormatting sqref="D322:D325">
     <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D322:D325">
+  <conditionalFormatting sqref="D326:D327">
     <cfRule type="duplicateValues" dxfId="15" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D322:D325">
+  <conditionalFormatting sqref="D326:D327">
     <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MASTER_MS5673.xlsx
+++ b/MASTER_MS5673.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Computer_CA\＊Strim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE831CF-04FA-44D0-A34C-8CD4DCCFC75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6E745E-8891-45D2-8444-EEA27F1CFC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="900" windowWidth="19815" windowHeight="13845" tabRatio="773" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
+    <workbookView xWindow="8115" yWindow="915" windowWidth="19815" windowHeight="13845" tabRatio="773" activeTab="1" xr2:uid="{0659EE3A-700C-4BA5-8BA7-8A59FA9E8EB8}"/>
   </bookViews>
   <sheets>
     <sheet name="MASTER" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Sheet3" sheetId="14" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MASTER!$A$1:$M$1160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MASTER!$A$1:$M$1172</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PWC &amp; 한영 확인'!$A$1:$N$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">심사_HSCODE!$A$1:$C$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">인증리스트!$A$1:$I$371</definedName>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10606" uniqueCount="4746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10727" uniqueCount="4801">
   <si>
     <t>무역거래처상호</t>
   </si>
@@ -16727,6 +16727,196 @@
   </si>
   <si>
     <t>MSF-073174</t>
+  </si>
+  <si>
+    <t>MSF-119141 (3KV142-401)</t>
+  </si>
+  <si>
+    <t>SEAGATE-HDD,3.5 IN,SATA,20TB,7 MODEL:STL027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-119141 (3KV142-401)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-119141</t>
+  </si>
+  <si>
+    <t>MSF-080039 (M1276599-001)</t>
+  </si>
+  <si>
+    <t>QUANTA-PCBA+MECH,MAIN BOARD,J2</t>
+  </si>
+  <si>
+    <t>MSF-080039 (M1276599-001)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-080039</t>
+  </si>
+  <si>
+    <t>MSF-111600 (M1205304-004)</t>
+  </si>
+  <si>
+    <t>LENOVO-PCBA+MECH,MOTHERBOARD,S</t>
+  </si>
+  <si>
+    <t>MSF-111600 (M1205304-004)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-111600</t>
+  </si>
+  <si>
+    <t>MSF-111599</t>
+  </si>
+  <si>
+    <t>MSF-111599 (M1205304-004)</t>
+  </si>
+  <si>
+    <t>ZT-PCBA+MECH,MOTHERBOARD,S2185</t>
+  </si>
+  <si>
+    <t>MSF-111599 (M1205304-004)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-064833 (M1023585-001)</t>
+  </si>
+  <si>
+    <t>QUANTA - PCBA,IO BOARD</t>
+  </si>
+  <si>
+    <t>MSF-064833 (M1023585-001)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-064833</t>
+  </si>
+  <si>
+    <t>MSF-073166 (M1215569-001)</t>
+  </si>
+  <si>
+    <t>MSF-073166 (M1215569-001)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073166</t>
+  </si>
+  <si>
+    <t>MSF-074894 (99C2DL)</t>
+  </si>
+  <si>
+    <t>MSF-074894 (99C2DL)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-074894</t>
+  </si>
+  <si>
+    <t>MSF-064826 (M1023580-002)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUANTA - PCBA,PDB DC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-064826</t>
+  </si>
+  <si>
+    <t>MSF-105728 (M1023578-002)</t>
+  </si>
+  <si>
+    <t>QUANTA-PCBA,POWER DISTRIBUTION</t>
+  </si>
+  <si>
+    <t>MSF-105728 (M1023578-002)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-105728</t>
+  </si>
+  <si>
+    <t>MSF-064832 (M1023603-001)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QUANTA - PCBA,FAN BOARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-064832</t>
+  </si>
+  <si>
+    <t>MSF-074884 (M1200247-002)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZT-PCBA+MECH,ACCESSORIES BOARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-074884</t>
+  </si>
+  <si>
+    <t>MSF-074881 (RMC74-2109)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-074881</t>
+  </si>
+  <si>
+    <t>MSF-073176 (RWHHW-N892)</t>
+  </si>
+  <si>
+    <t>AMPHENOL FIBER OPTIC PRODUCTS- VOLT:DC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073176 (RWHHW-N892)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073170 (RWHHW-N276)</t>
+  </si>
+  <si>
+    <t>AMPHENOL FIBER OPTIC PRODUCTS VOLT:~DC48V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073168 (RWHHW-H878)</t>
+  </si>
+  <si>
+    <t>MSF-073168 (RWHHW-H878)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073170 (RWHHW-N276)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073175 (RWHHW-N891)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPHENOL FIBER OPTIC PRODUCTS- </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073171 (RWHHW-N038)</t>
+  </si>
+  <si>
+    <t>AMPHENOL FIBER OPTIC PRODUCTS VOLT:DC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSF-073175</t>
+  </si>
+  <si>
+    <t>MSF-073171 (RWHHW-N038)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17200,7 +17390,327 @@
     <cellStyle name="표준 2" xfId="1" xr:uid="{04AB7DDF-CEE2-4E84-BB25-B76053D24319}"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
-  <dxfs count="94">
+  <dxfs count="126">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -18853,7 +19363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}">
-  <dimension ref="A1:N1171"/>
+  <dimension ref="A1:N1188"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
@@ -38944,7 +39454,7 @@
         <v>4733</v>
       </c>
     </row>
-    <row r="1169" spans="2:4">
+    <row r="1169" spans="2:6">
       <c r="B1169" s="1" t="s">
         <v>3302</v>
       </c>
@@ -38955,7 +39465,7 @@
         <v>4735</v>
       </c>
     </row>
-    <row r="1170" spans="2:4">
+    <row r="1170" spans="2:6">
       <c r="B1170" s="1" t="s">
         <v>3406</v>
       </c>
@@ -38966,7 +39476,7 @@
         <v>4741</v>
       </c>
     </row>
-    <row r="1171" spans="2:4">
+    <row r="1171" spans="2:6">
       <c r="B1171" s="1" t="s">
         <v>3406</v>
       </c>
@@ -38977,45 +39487,238 @@
         <v>4743</v>
       </c>
     </row>
+    <row r="1172" spans="2:6">
+      <c r="B1172" s="1" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>4746</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>4747</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>4165</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="1173" spans="2:6">
+      <c r="B1173" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>4750</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="1174" spans="2:6">
+      <c r="B1174" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>4754</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="1175" spans="2:6">
+      <c r="B1175" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>4759</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="1176" spans="2:6">
+      <c r="B1176" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>4762</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="1177" spans="2:6">
+      <c r="B1177" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>4766</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1178" spans="2:6">
+      <c r="B1178" s="1" t="s">
+        <v>3318</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>4769</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1179" spans="2:6">
+      <c r="B1179" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>4772</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="1180" spans="2:6">
+      <c r="B1180" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>4775</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>4776</v>
+      </c>
+    </row>
+    <row r="1181" spans="2:6">
+      <c r="B1181" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>4779</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="1182" spans="2:6">
+      <c r="B1182" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>4782</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="1183" spans="2:6">
+      <c r="B1183" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>4785</v>
+      </c>
+      <c r="D1183" t="s">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="1184" spans="2:6">
+      <c r="B1184" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>4787</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="1185" spans="2:4">
+      <c r="B1185" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>4790</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>4791</v>
+      </c>
+    </row>
+    <row r="1186" spans="2:4">
+      <c r="B1186" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>4792</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="1187" spans="2:4">
+      <c r="B1187" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>4795</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>4796</v>
+      </c>
+    </row>
+    <row r="1188" spans="2:4">
+      <c r="B1188" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>4797</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>4798</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1160" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}"/>
+  <autoFilter ref="A1:M1172" xr:uid="{AA1AB1B7-4662-4C58-9F56-BB8ACFA1530D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C995">
-    <cfRule type="duplicateValues" dxfId="93" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C996">
-    <cfRule type="duplicateValues" dxfId="92" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C2:C992 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="91" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C997:C1005 C1007:C1014 D1006 C994 C1016:C1046 D1092:D1094 D1096:D1097 C1048:C1111 C1113:C1117 C1119:C1124 C1126 C1128:C1136 C1138:C1048576">
-    <cfRule type="duplicateValues" dxfId="90" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1118">
-    <cfRule type="duplicateValues" dxfId="89" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1127">
-    <cfRule type="duplicateValues" dxfId="88" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1137">
-    <cfRule type="duplicateValues" dxfId="87" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E709">
-    <cfRule type="duplicateValues" dxfId="86" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E769">
-    <cfRule type="duplicateValues" dxfId="84" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E788">
-    <cfRule type="duplicateValues" dxfId="82" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E832">
-    <cfRule type="duplicateValues" dxfId="80" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -39227,7 +39930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDB924F-9221-4917-B11B-3326F8C1F68D}">
-  <dimension ref="A1:N327"/>
+  <dimension ref="A1:N344"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
@@ -45724,153 +46427,487 @@
         <v>4743</v>
       </c>
     </row>
+    <row r="328" spans="2:5">
+      <c r="B328" s="1" t="s">
+        <v>3546</v>
+      </c>
+      <c r="C328" t="s">
+        <v>4749</v>
+      </c>
+      <c r="D328" t="s">
+        <v>4748</v>
+      </c>
+      <c r="E328" t="s">
+        <v>4747</v>
+      </c>
+    </row>
+    <row r="329" spans="2:5">
+      <c r="B329" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C329" t="s">
+        <v>4753</v>
+      </c>
+      <c r="D329" t="s">
+        <v>4752</v>
+      </c>
+      <c r="E329" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="330" spans="2:5">
+      <c r="B330" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C330" t="s">
+        <v>4757</v>
+      </c>
+      <c r="D330" t="s">
+        <v>4756</v>
+      </c>
+      <c r="E330" t="s">
+        <v>4755</v>
+      </c>
+    </row>
+    <row r="331" spans="2:5">
+      <c r="B331" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C331" t="s">
+        <v>4758</v>
+      </c>
+      <c r="D331" t="s">
+        <v>4761</v>
+      </c>
+      <c r="E331" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="332" spans="2:5">
+      <c r="B332" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C332" t="s">
+        <v>4765</v>
+      </c>
+      <c r="D332" t="s">
+        <v>4764</v>
+      </c>
+      <c r="E332" t="s">
+        <v>4763</v>
+      </c>
+    </row>
+    <row r="333" spans="2:5">
+      <c r="B333" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C333" t="s">
+        <v>4768</v>
+      </c>
+      <c r="D333" t="s">
+        <v>4767</v>
+      </c>
+      <c r="E333" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="334" spans="2:5">
+      <c r="B334" s="1" t="s">
+        <v>3318</v>
+      </c>
+      <c r="C334" t="s">
+        <v>4771</v>
+      </c>
+      <c r="D334" t="s">
+        <v>4770</v>
+      </c>
+      <c r="E334" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="335" spans="2:5">
+      <c r="B335" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C335" t="s">
+        <v>4774</v>
+      </c>
+      <c r="D335" t="s">
+        <v>4772</v>
+      </c>
+      <c r="E335" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="336" spans="2:5">
+      <c r="B336" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C336" t="s">
+        <v>4778</v>
+      </c>
+      <c r="D336" t="s">
+        <v>4777</v>
+      </c>
+      <c r="E336" t="s">
+        <v>4776</v>
+      </c>
+    </row>
+    <row r="337" spans="2:5">
+      <c r="B337" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C337" t="s">
+        <v>4781</v>
+      </c>
+      <c r="D337" t="s">
+        <v>4779</v>
+      </c>
+      <c r="E337" t="s">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="338" spans="2:5">
+      <c r="B338" s="1" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C338" t="s">
+        <v>4784</v>
+      </c>
+      <c r="D338" t="s">
+        <v>4782</v>
+      </c>
+      <c r="E338" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="339" spans="2:5">
+      <c r="B339" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C339" t="s">
+        <v>4786</v>
+      </c>
+      <c r="D339" t="s">
+        <v>4785</v>
+      </c>
+      <c r="E339" t="s">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="340" spans="2:5">
+      <c r="B340" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C340" t="s">
+        <v>4545</v>
+      </c>
+      <c r="D340" t="s">
+        <v>4789</v>
+      </c>
+      <c r="E340" t="s">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="341" spans="2:5">
+      <c r="B341" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C341" t="s">
+        <v>4553</v>
+      </c>
+      <c r="D341" t="s">
+        <v>4793</v>
+      </c>
+      <c r="E341" t="s">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="342" spans="2:5">
+      <c r="B342" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C342" t="s">
+        <v>4704</v>
+      </c>
+      <c r="D342" t="s">
+        <v>4794</v>
+      </c>
+      <c r="E342" t="s">
+        <v>4791</v>
+      </c>
+    </row>
+    <row r="343" spans="2:5">
+      <c r="B343" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C343" t="s">
+        <v>4799</v>
+      </c>
+      <c r="D343" t="s">
+        <v>4795</v>
+      </c>
+      <c r="E343" t="s">
+        <v>4796</v>
+      </c>
+    </row>
+    <row r="344" spans="2:5">
+      <c r="B344" s="1" t="s">
+        <v>3369</v>
+      </c>
+      <c r="C344" t="s">
+        <v>4547</v>
+      </c>
+      <c r="D344" t="s">
+        <v>4800</v>
+      </c>
+      <c r="E344" t="s">
+        <v>4798</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D2:D265">
-    <cfRule type="duplicateValues" dxfId="78" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D271:D278 D267:D269 E266 D259:D265">
-    <cfRule type="duplicateValues" dxfId="77" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D279">
-    <cfRule type="duplicateValues" dxfId="76" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D281">
-    <cfRule type="duplicateValues" dxfId="74" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D286">
-    <cfRule type="duplicateValues" dxfId="72" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D287:D288">
-    <cfRule type="duplicateValues" dxfId="70" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D290">
-    <cfRule type="duplicateValues" dxfId="68" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D292">
-    <cfRule type="duplicateValues" dxfId="66" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D293">
-    <cfRule type="duplicateValues" dxfId="64" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D294">
-    <cfRule type="duplicateValues" dxfId="62" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D295">
-    <cfRule type="duplicateValues" dxfId="60" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D296">
-    <cfRule type="duplicateValues" dxfId="58" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D298">
-    <cfRule type="duplicateValues" dxfId="56" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D299">
-    <cfRule type="duplicateValues" dxfId="54" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D300">
-    <cfRule type="duplicateValues" dxfId="52" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D301">
+    <cfRule type="duplicateValues" dxfId="82" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D302">
+    <cfRule type="duplicateValues" dxfId="81" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D303">
+    <cfRule type="duplicateValues" dxfId="79" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D304">
+    <cfRule type="duplicateValues" dxfId="77" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D306">
+    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D308">
+    <cfRule type="duplicateValues" dxfId="73" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D310">
+    <cfRule type="duplicateValues" dxfId="71" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D311">
+    <cfRule type="duplicateValues" dxfId="69" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D312">
+    <cfRule type="duplicateValues" dxfId="67" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D313">
+    <cfRule type="duplicateValues" dxfId="65" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D314">
+    <cfRule type="duplicateValues" dxfId="63" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D315">
+    <cfRule type="duplicateValues" dxfId="61" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="59" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C316:D316">
+    <cfRule type="duplicateValues" dxfId="58" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D317">
+    <cfRule type="duplicateValues" dxfId="57" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D317">
+    <cfRule type="duplicateValues" dxfId="56" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D318">
+    <cfRule type="duplicateValues" dxfId="55" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D318">
+    <cfRule type="duplicateValues" dxfId="54" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D319">
+    <cfRule type="duplicateValues" dxfId="53" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D319">
+    <cfRule type="duplicateValues" dxfId="52" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D320:D321">
+    <cfRule type="duplicateValues" dxfId="51" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D320:D321">
     <cfRule type="duplicateValues" dxfId="50" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D302">
-    <cfRule type="duplicateValues" dxfId="49" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
+  <conditionalFormatting sqref="D322:D325">
+    <cfRule type="duplicateValues" dxfId="49" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D303">
-    <cfRule type="duplicateValues" dxfId="47" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="34"/>
+  <conditionalFormatting sqref="D322:D325">
+    <cfRule type="duplicateValues" dxfId="48" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D304">
-    <cfRule type="duplicateValues" dxfId="45" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
+  <conditionalFormatting sqref="D326:D327">
+    <cfRule type="duplicateValues" dxfId="47" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D306">
-    <cfRule type="duplicateValues" dxfId="43" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+  <conditionalFormatting sqref="D326:D327">
+    <cfRule type="duplicateValues" dxfId="46" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D308">
-    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="28"/>
+  <conditionalFormatting sqref="D328">
+    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D310">
-    <cfRule type="duplicateValues" dxfId="39" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="26"/>
+  <conditionalFormatting sqref="D328">
+    <cfRule type="duplicateValues" dxfId="44" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D311">
-    <cfRule type="duplicateValues" dxfId="37" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
+  <conditionalFormatting sqref="D329">
+    <cfRule type="duplicateValues" dxfId="43" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D312">
-    <cfRule type="duplicateValues" dxfId="35" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="22"/>
+  <conditionalFormatting sqref="D329">
+    <cfRule type="duplicateValues" dxfId="42" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D313">
-    <cfRule type="duplicateValues" dxfId="33" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="20"/>
+  <conditionalFormatting sqref="D330">
+    <cfRule type="duplicateValues" dxfId="41" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D314">
-    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="18"/>
+  <conditionalFormatting sqref="D330">
+    <cfRule type="duplicateValues" dxfId="40" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D315">
-    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
+  <conditionalFormatting sqref="D331">
+    <cfRule type="duplicateValues" dxfId="39" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C316:D316">
+  <conditionalFormatting sqref="D331">
+    <cfRule type="duplicateValues" dxfId="38" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D332">
+    <cfRule type="duplicateValues" dxfId="37" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D332">
+    <cfRule type="duplicateValues" dxfId="36" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D333">
+    <cfRule type="duplicateValues" dxfId="35" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D333">
+    <cfRule type="duplicateValues" dxfId="34" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D334">
+    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D334">
+    <cfRule type="duplicateValues" dxfId="32" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D335">
+    <cfRule type="duplicateValues" dxfId="31" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D335">
+    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D336">
+    <cfRule type="duplicateValues" dxfId="29" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D336">
+    <cfRule type="duplicateValues" dxfId="28" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D337">
     <cfRule type="duplicateValues" dxfId="27" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C316:D316">
+  <conditionalFormatting sqref="D337">
     <cfRule type="duplicateValues" dxfId="26" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D317">
+  <conditionalFormatting sqref="D338">
     <cfRule type="duplicateValues" dxfId="25" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D317">
+  <conditionalFormatting sqref="D338">
     <cfRule type="duplicateValues" dxfId="24" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318">
+  <conditionalFormatting sqref="D339">
     <cfRule type="duplicateValues" dxfId="23" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D318">
+  <conditionalFormatting sqref="D339">
     <cfRule type="duplicateValues" dxfId="22" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D319">
+  <conditionalFormatting sqref="D340">
     <cfRule type="duplicateValues" dxfId="21" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D319">
+  <conditionalFormatting sqref="D340">
     <cfRule type="duplicateValues" dxfId="20" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D320:D321">
+  <conditionalFormatting sqref="D341">
     <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D320:D321">
+  <conditionalFormatting sqref="D341">
     <cfRule type="duplicateValues" dxfId="18" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D322:D325">
+  <conditionalFormatting sqref="D342">
     <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D322:D325">
+  <conditionalFormatting sqref="D342">
     <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D326:D327">
+  <conditionalFormatting sqref="D343:D344">
     <cfRule type="duplicateValues" dxfId="15" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D326:D327">
+  <conditionalFormatting sqref="D343:D344">
     <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
